--- a/01_data/01_input_data/02_processed/LNG_Transportation_Cost_Calculation.xlsx
+++ b/01_data/01_input_data/02_processed/LNG_Transportation_Cost_Calculation.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C9D50D-DE0A-4072-AC99-3A760B754A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A579C15-24CA-4556-AB34-448BB37E22C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{24B830EA-0063-4094-B37E-F92C9074D879}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="135">
   <si>
     <t>Euro to Dollar</t>
   </si>
@@ -426,6 +426,24 @@
   </si>
   <si>
     <t>Cost Suez per GWh</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Pipeline cost upper</t>
+  </si>
+  <si>
+    <t>Pipeline cost lower</t>
+  </si>
+  <si>
+    <t>Dollar/MMBtu/1000km</t>
+  </si>
+  <si>
+    <t>pipeline transport cost</t>
+  </si>
+  <si>
+    <t>cost pipe per GWh and km</t>
   </si>
 </sst>
 </file>
@@ -798,55 +816,72 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E636EF09-FB65-4BB4-9513-8116EABFF6AD}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.81640625" customWidth="1"/>
+    <col min="1" max="1" width="22.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1">
-        <f>LNG_Cost_raw!B30</f>
-        <v>8.0496656242732792E-2</v>
+        <v>129</v>
+      </c>
+      <c r="B1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B2">
-        <f>LNG_Cost_raw!B31</f>
-        <v>8530.3536997424526</v>
+        <f>LNG_Cost_raw!B33</f>
+        <v>8.0496656242732792E-2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B3">
-        <f>LNG_Cost_raw!B32</f>
-        <v>2217.8919619330377</v>
+        <f>LNG_Cost_raw!B34</f>
+        <v>8530.3536997424526</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B4">
-        <f>LNG_Cost_raw!B33</f>
-        <v>1000</v>
+        <f>LNG_Cost_raw!B35</f>
+        <v>2217.8919619330377</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5">
+        <f>LNG_Cost_raw!B36</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>128</v>
       </c>
-      <c r="B5">
-        <f>LNG_Cost_raw!B34</f>
+      <c r="B6">
+        <f>LNG_Cost_raw!B37</f>
         <v>950</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7">
+        <f>LNG_Cost_raw!B39</f>
+        <v>1.7060707399484905</v>
       </c>
     </row>
   </sheetData>
@@ -856,7 +891,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C67DCBF-103E-42D2-98E0-69A31DB057CA}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.54296875" customWidth="1"/>
@@ -966,101 +1001,90 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="1">
-        <v>3</v>
+        <v>130</v>
+      </c>
+      <c r="B11">
+        <v>2.5</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="1">
-        <v>2</v>
+        <v>131</v>
+      </c>
+      <c r="B12">
+        <v>0.5</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14">
-        <v>0.3</v>
+        <v>39</v>
+      </c>
+      <c r="B14" s="1">
+        <v>3</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+    </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="B16">
-        <v>2.9307108333332998E-4</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="B17">
-        <v>14447.204969443999</v>
+        <v>0.3</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18">
-        <v>6250</v>
-      </c>
-      <c r="C18" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B19">
-        <v>50</v>
+        <v>2.9307108333332998E-4</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B20">
-        <v>450</v>
+        <v>14447.204969443999</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -1068,11 +1092,10 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <f>B19*B20</f>
-        <v>22500</v>
+        <v>6250</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -1080,127 +1103,173 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <f>B21/B23</f>
-        <v>6.2500000000000003E-3</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
       <c r="B23">
-        <v>3600000</v>
+        <v>450</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24">
+        <f>B22*B23</f>
+        <v>22500</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25">
+        <f>B24/B26</f>
+        <v>6.2500000000000003E-3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B26">
+        <v>3600000</v>
+      </c>
+      <c r="C26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>26</v>
       </c>
-      <c r="B25">
-        <f>B3*B22</f>
+      <c r="B28">
+        <f>B3*B25</f>
         <v>1000</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C28" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>5</v>
       </c>
-      <c r="B26">
+      <c r="B29">
         <f>B5*B6</f>
         <v>31.484000000000002</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C29" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27">
-        <f>B26*24</f>
-        <v>755.61599999999999</v>
-      </c>
-      <c r="C27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28">
-        <f>(B4/B1)/B25</f>
-        <v>60.824561403508781</v>
-      </c>
-      <c r="C28" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B30">
-        <f>B28/B27</f>
-        <v>8.0496656242732792E-2</v>
+        <f>B29*24</f>
+        <v>755.61599999999999</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B31">
-        <f>1/B16*AVERAGE(B11:B12)</f>
-        <v>8530.3536997424526</v>
+        <f>(B4/B1)/B28</f>
+        <v>60.824561403508781</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32">
-        <f>1/B16*AVERAGE(B13:B14)</f>
-        <v>2217.8919619330377</v>
-      </c>
-      <c r="C32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B33">
-        <f>B8/$B$25</f>
-        <v>1000</v>
+        <f>B31/B30</f>
+        <v>8.0496656242732792E-2</v>
       </c>
       <c r="C33" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B34">
-        <f>B9/$B$25</f>
-        <v>950</v>
+        <f>1/B19*AVERAGE(B14:B15)</f>
+        <v>8530.3536997424526</v>
       </c>
       <c r="C34" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35">
+        <f>1/B19*AVERAGE(B16:B17)</f>
+        <v>2217.8919619330377</v>
+      </c>
+      <c r="C35" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36">
+        <f>B8/$B$28</f>
+        <v>1000</v>
+      </c>
+      <c r="C36" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37">
+        <f>B9/$B$28</f>
+        <v>950</v>
+      </c>
+      <c r="C37" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>133</v>
+      </c>
+      <c r="B39">
+        <f>B12/1000/B19</f>
+        <v>1.7060707399484905</v>
+      </c>
+      <c r="C39" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1760,7 +1829,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="C2" s="1">
-        <f>B2*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$16</f>
+        <f>B2*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$19</f>
         <v>19060.222306704538</v>
       </c>
       <c r="D2">
@@ -1775,7 +1844,7 @@
         <v>7.5</v>
       </c>
       <c r="C3" s="1">
-        <f>B3*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$16</f>
+        <f>B3*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$19</f>
         <v>29173.809653119184</v>
       </c>
       <c r="D3">
@@ -1790,7 +1859,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="1">
-        <f>B4*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$16</f>
+        <f>B4*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$19</f>
         <v>23339.04772249535</v>
       </c>
       <c r="D4">
@@ -1805,7 +1874,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="1">
-        <f>B5*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$16</f>
+        <f>B5*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$19</f>
         <v>23339.04772249535</v>
       </c>
       <c r="D5">
@@ -1820,7 +1889,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C6" s="1">
-        <f>B6*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$16</f>
+        <f>B6*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$19</f>
         <v>15948.349277038487</v>
       </c>
       <c r="D6">
@@ -1835,7 +1904,7 @@
         <v>3.7</v>
       </c>
       <c r="C7" s="1">
-        <f>B7*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$16</f>
+        <f>B7*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$19</f>
         <v>14392.412762205466</v>
       </c>
       <c r="D7">
@@ -1850,7 +1919,7 @@
         <v>4.5</v>
       </c>
       <c r="C8" s="1">
-        <f>B8*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$16</f>
+        <f>B8*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$19</f>
         <v>17504.285791871513</v>
       </c>
       <c r="D8">
@@ -1865,7 +1934,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="1">
-        <f>B9*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$16</f>
+        <f>B9*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$19</f>
         <v>23339.04772249535</v>
       </c>
       <c r="D9">
@@ -1880,7 +1949,7 @@
         <v>8.4</v>
       </c>
       <c r="C10" s="1">
-        <f>B10*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$16</f>
+        <f>B10*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$19</f>
         <v>32674.666811493484</v>
       </c>
       <c r="D10">
@@ -1895,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="1">
-        <f>B11*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$16</f>
+        <f>B11*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$19</f>
         <v>19449.206435412791</v>
       </c>
       <c r="D11">
@@ -1910,7 +1979,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="1">
-        <f>B12*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$16</f>
+        <f>B12*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$19</f>
         <v>11669.523861247675</v>
       </c>
       <c r="D12">
@@ -1925,7 +1994,7 @@
         <v>2.4</v>
       </c>
       <c r="C13" s="1">
-        <f>B13*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$16</f>
+        <f>B13*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$19</f>
         <v>9335.619088998139</v>
       </c>
       <c r="D13">
@@ -1940,7 +2009,7 @@
         <v>4.5</v>
       </c>
       <c r="C14" s="1">
-        <f>B14*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$16</f>
+        <f>B14*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$19</f>
         <v>17504.285791871513</v>
       </c>
       <c r="D14">
@@ -1955,7 +2024,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C15" s="1">
-        <f>B15*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$16</f>
+        <f>B15*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$19</f>
         <v>19838.190564121043</v>
       </c>
       <c r="D15">
@@ -1970,7 +2039,7 @@
         <v>5.9</v>
       </c>
       <c r="C16" s="1">
-        <f>B16*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$16</f>
+        <f>B16*LNG_Cost_raw!$B$1/LNG_Cost_raw!$B$19</f>
         <v>22950.063593787094</v>
       </c>
       <c r="D16">
